--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3764,6 +3764,438 @@
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Packaged; Sun dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Honey</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Korean fried chicken honey soy sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Toasted sesame seeds</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Spice rack</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Garnish for Korean wings</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Palm sugar</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Thai pandan chicken marinade</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Bay leaves</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Spice rack</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Beef stew</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Italian herbs / Italian seasoning</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Spice rack</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Beef stew</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Dried scallops</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Steamed egg tofu, soups</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Dried shrimp</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sambal kangkong, sambal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ikan bilis (dried anchovies)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Nasi lemak side</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Dried chillies</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sambal kangkong, sambal</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Raw peanuts (unsalted)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Lotus root soup, nasi lemak</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Beef broth / stock (carton)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Beef stew</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Red wine (cooking)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Beef stew braising liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Shallots</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Pandan chicken, sambal</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sake (cooking)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Japanese mushroom rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Japanese short-grain rice</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Japanese mushroom rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sea salt flakes</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Spice rack</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Japanese mushroom rice finishing</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4196,6 +4196,195 @@
       <c r="H137" t="inlineStr">
         <is>
           <t>Japanese mushroom rice finishing</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Anchovy powder</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Fishball minced pork soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Whole white peppercorns</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Ban mian / mee hoon kway broth</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Dried soya beans (whole)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Ban mian / mee hoon kway broth</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Rock sugar</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sticky pork belly braise</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Jin hua ham 金华火腿</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Yang Zhou fried rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Black bean paste</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Claypot tofu</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Scallops</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Cheesy baked rice</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -95,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,6 +111,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4385,6 +4388,606 @@
       <c r="H144" t="inlineStr">
         <is>
           <t>Cheesy baked rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Lap cheong (Chinese sausage)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Fri HK steamed chicken rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Fermented black beans 豆豉</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Fri chicken rice marinade</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Chiu chow chilli oil</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Fri chicken rice, to serve</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Fish cakes</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Mon prawn noodle soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Instant noodles (ramen blocks)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>46179</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Thu stir-fry beef ramen</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>White miso</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tonjiru</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Gobo (burdock root)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Tonjiru — can omit</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Dried sole fish (flounder)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Seafood pao fan broth</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Shabu shabu beef (sliced)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Pepper lunch beef rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Canned sweetcorn</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Pepper lunch beef rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Coarse black pepper</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Pepper lunch beef rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Chicken feet</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Seafood pao fan broth</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Fresh flat rice noodles (kway teow)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Wat Tan Hor Fun</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Mee tai bak (silver needle noodles)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Mon claypot mee tai bak</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Watercress</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Mon watercress pork rib soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Glass vermicelli (tanghoon)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Hainanese chap chye</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Round cabbage</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Hainanese chap chye</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Shimeji mushrooms</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Wed shimeji spinach tofu</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Unsweetened soya bean milk</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Wed homemade egg tofu</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Okra (lady's fingers)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Wed stir-fried veg with dried shrimp</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4988,6 +4988,336 @@
       <c r="H164" t="inlineStr">
         <is>
           <t>Wed stir-fried veg with dried shrimp</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Gochujang (Korean chilli paste)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Wed gochujang noodles</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Gochugaru (Korean chilli flakes)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Wed gochujang noodles</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sesame paste (tahini)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Wed gochujang noodles</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Korean knife-cut noodles</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Wed gochujang noodles</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Pancetta</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Mon bolognese</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Passata (Italian tomato)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Mon bolognese</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Peeled tomatoes (can)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Mon bolognese</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Kidney beans (can)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sun minestrone</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Chinese yam (山药)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Mon yam chicken soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Char siew</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Wed Sin Chew bee hoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Thai sweet chilli sauce</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Thu fried fish</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5318,6 +5318,216 @@
       <c r="H175" t="inlineStr">
         <is>
           <t>Thu fried fish</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Minced beef</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sun shepherd's pie (beef)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Gruyère cheese</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Fri aligot</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Port Salut cheese</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Fri aligot</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Pecorino cheese</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sun shepherd's pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Panko breadcrumbs</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sun shepherd's pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Lemon pepper seasoning</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Mon oven baked chicken leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Japanese curry cubes</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Wed Japanese curry</t>
         </is>
       </c>
     </row>
